--- a/ensayos/f5/presupuestos/P-2026-002.xlsx
+++ b/ensayos/f5/presupuestos/P-2026-002.xlsx
@@ -257,12 +257,12 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arte e ilustración</t>
+          <t xml:space="preserve">Arte (props)</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilustración o cuadro</t>
+          <t xml:space="preserve">Prop</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -272,40 +272,40 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">compleja</t>
+          <t xml:space="preserve">muy alta</t>
         </is>
       </c>
       <c r="E8" s="0">
         <v>1</v>
       </c>
       <c r="F8" s="5">
-        <v>28.8</v>
+        <v>2.5</v>
       </c>
       <c r="G8" s="4">
         <v>30</v>
       </c>
       <c r="H8" s="4">
         <f>F8*G8</f>
-        <v>864</v>
+        <v>75</v>
       </c>
       <c r="I8" s="5">
         <f>E8*F8</f>
-        <v>28.8</v>
+        <v>2.5</v>
       </c>
       <c r="J8" s="4">
         <f>E8*H8</f>
-        <v>864</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arte e ilustración</t>
+          <t xml:space="preserve">Arte (props)</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objeto o asset pequeño</t>
+          <t xml:space="preserve">Prop</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -322,33 +322,33 @@
         <v>1</v>
       </c>
       <c r="F9" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4">
         <v>30</v>
       </c>
       <c r="H9" s="4">
         <f>F9*G9</f>
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I9" s="5">
         <f>E9*F9</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4">
         <f>E9*H9</f>
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arte e ilustración</t>
+          <t xml:space="preserve">Arte (props)</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Icono</t>
+          <t xml:space="preserve">Prop</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -358,201 +358,201 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">sencilla</t>
+          <t xml:space="preserve">baja</t>
         </is>
       </c>
       <c r="E10" s="0">
         <v>3</v>
       </c>
       <c r="F10" s="5">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="4">
         <v>30</v>
       </c>
       <c r="H10" s="4">
         <f>F10*G10</f>
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I10" s="5">
         <f>E10*F10</f>
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J10" s="4">
         <f>E10*H10</f>
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diseño y maquetación</t>
+          <t xml:space="preserve">Arte (props)</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Página nueva</t>
+          <t xml:space="preserve">Prop</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Página «Prueba 3: el cuadro de la fiesta» con el cuadro, la tarta y la ficha de respuestas</t>
+          <t xml:space="preserve">Polaroid del expediente con un marco de fiesta (confeti y globos)</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">media</t>
+          <t xml:space="preserve">baja</t>
         </is>
       </c>
       <c r="E11" s="0">
         <v>1</v>
       </c>
       <c r="F11" s="5">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H11" s="4">
         <f>F11*G11</f>
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="I11" s="5">
         <f>E11*F11</f>
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J11" s="4">
         <f>E11*H11</f>
-        <v>70</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diseño y maquetación</t>
+          <t xml:space="preserve">Maquetación</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajuste de una página existente</t>
+          <t xml:space="preserve">Maquetación</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prueba final y hoja de quien dirige la misión: la nueva contraseña y la numeración de pruebas</t>
+          <t xml:space="preserve">Página nueva «Prueba 3: el cuadro de la fiesta», y la prueba final y la hoja de quien dirige con la nueva contraseña</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">media</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E12" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="G12" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H12" s="4">
         <f>F12*G12</f>
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="I12" s="5">
         <f>E12*F12</f>
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J12" s="4">
         <f>E12*H12</f>
-        <v>42</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diseño y maquetación</t>
+          <t xml:space="preserve">Game design</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Textos de una página (ES/EN)</t>
+          <t xml:space="preserve">Game design de un puzzle</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Textos de la página nueva en español e inglés</t>
+          <t xml:space="preserve">El cuadro de la fiesta: qué objetos se esconden, sus pistas y cómo dan la contraseña</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">media</t>
+          <t xml:space="preserve">medio</t>
         </is>
       </c>
       <c r="E13" s="0">
         <v>1</v>
       </c>
       <c r="F13" s="5">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="G13" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H13" s="4">
         <f>F13*G13</f>
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="I13" s="5">
         <f>E13*F13</f>
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J13" s="4">
         <f>E13*H13</f>
-        <v>28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diseño y maquetación</t>
+          <t xml:space="preserve">Game design</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pregunta del formulario</t>
+          <t xml:space="preserve">Game design: testing</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pregunta nueva del formulario: comida favorita del cumpleañero (sale en el cuadro)</t>
+          <t xml:space="preserve">Partida completa con el juego impreso</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">media</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E14" s="0">
         <v>1</v>
       </c>
       <c r="F14" s="5">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="G14" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H14" s="4">
         <f>F14*G14</f>
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="I14" s="5">
         <f>E14*F14</f>
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J14" s="4">
         <f>E14*H14</f>
-        <v>14</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
@@ -563,7 +563,7 @@
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mecánica nueva sencilla</t>
+          <t xml:space="preserve">Programación de un puzzle</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -573,238 +573,195 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">media</t>
+          <t xml:space="preserve">medio</t>
         </is>
       </c>
       <c r="E15" s="0">
         <v>1</v>
       </c>
       <c r="F15" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G15" s="4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H15" s="4">
         <f>F15*G15</f>
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="I15" s="5">
         <f>E15*F15</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4">
         <f>E15*H15</f>
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pruebas</t>
+          <t xml:space="preserve">Programación</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prueba de un puzzle</t>
+          <t xml:space="preserve">Programación: ajustes</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolver la prueba nueva en papel con dos nombres distintos</t>
+          <t xml:space="preserve">Pregunta nueva del formulario: comida favorita del cumpleañero (sale en el cuadro)</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">media</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E16" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="5">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G16" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H16" s="4">
         <f>F16*G16</f>
-        <v>18.75</v>
+        <v>50</v>
       </c>
       <c r="I16" s="5">
         <f>E16*F16</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J16" s="4">
         <f>E16*H16</f>
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pruebas</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prueba completa del juego</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Partida completa con el juego impreso</t>
-        </is>
-      </c>
-      <c r="D17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sencilla</t>
-        </is>
-      </c>
-      <c r="E17" s="0">
-        <v>1</v>
-      </c>
-      <c r="F17" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="G17" s="4">
-        <v>25</v>
-      </c>
-      <c r="H17" s="4">
-        <f>F17*G17</f>
-        <v>45</v>
-      </c>
-      <c r="I17" s="5">
-        <f>E17*F17</f>
-        <v>1.8</v>
-      </c>
-      <c r="J17" s="4">
-        <f>E17*H17</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Base</t>
+        </is>
+      </c>
+      <c r="J18" s="6">
+        <f>SUM(J8:J16)</f>
+        <v>660</v>
+      </c>
+    </row>
     <row r="19">
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Base</t>
-        </is>
-      </c>
-      <c r="J19" s="6">
-        <f>SUM(J8:J17)</f>
-        <v>1511.5</v>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horas totales</t>
+        </is>
+      </c>
+      <c r="J19" s="5">
+        <f>SUM(I8:I16)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coordinación y gestión</t>
+        </is>
+      </c>
+      <c r="H20" s="7">
+        <v>0</v>
+      </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horas totales</t>
-        </is>
-      </c>
-      <c r="J20" s="5">
-        <f>SUM(I8:I17)</f>
-        <v>49.3</v>
+          <t xml:space="preserve">Gestión</t>
+        </is>
+      </c>
+      <c r="J20" s="4">
+        <f>J18*H20/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coordinación y gestión</t>
+          <t xml:space="preserve">Descuento</t>
         </is>
       </c>
       <c r="H21" s="7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestión</t>
+          <t xml:space="preserve">Descuento</t>
         </is>
       </c>
       <c r="J21" s="4">
-        <f>J19*H21/100</f>
-        <v>151.15</v>
+        <f>-(J18+J20)*H21/100</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Descuento</t>
-        </is>
-      </c>
-      <c r="H22" s="7">
-        <v>0</v>
-      </c>
-      <c r="I22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Descuento</t>
-        </is>
-      </c>
-      <c r="J22" s="4">
-        <f>-(J19+J21)*H22/100</f>
-        <v>0</v>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Base imponible</t>
+        </is>
+      </c>
+      <c r="J22" s="6">
+        <f>J18+J20+J21</f>
+        <v>660</v>
       </c>
     </row>
     <row r="23">
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Base imponible</t>
-        </is>
-      </c>
-      <c r="J23" s="6">
-        <f>J19+J21+J22</f>
-        <v>1662.65</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="G24" s="0" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">IVA</t>
         </is>
       </c>
-      <c r="H24" s="7">
+      <c r="H23" s="7">
         <v>21</v>
       </c>
-      <c r="I24" s="0" t="inlineStr">
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">IVA</t>
         </is>
       </c>
-      <c r="J24" s="4">
-        <f>J23*H24/100</f>
-        <v>349.16</v>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="I25" s="1" t="inlineStr">
+      <c r="J23" s="4">
+        <f>J22*H23/100</f>
+        <v>138.6</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">TOTAL</t>
         </is>
       </c>
-      <c r="J25" s="9">
-        <f>J23+J24</f>
-        <v>2011.81</v>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="J24" s="9">
+        <f>J22+J23</f>
+        <v>798.6</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Condiciones</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="72" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Validez del presupuesto: 30 días. Cada pieza de arte incluye boceto y dos rondas de cambios; los cambios adicionales se presupuestan aparte. Pago: 50 % al aceptar y 50 % a la entrega. Plazo orientativo: a convenir al aceptar. Las piezas de arte quedan en la biblioteca del estudio y el cliente tiene licencia de uso para este juego.</t>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validez del presupuesto: 30 días. Cada prop incluye boceto y dos rondas de cambios; los cambios adicionales se presupuestan aparte. Pago: 50 % al aceptar y 50 % a la entrega. Plazo orientativo: a convenir al aceptar. Las piezas de arte quedan en la biblioteca del estudio y el cliente tiene licencia de uso para este juego.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A27:J27"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -814,10 +771,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="80" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="80" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -842,7 +799,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilustración</t>
+          <t xml:space="preserve">Arte (props)</t>
         </is>
       </c>
       <c r="B3" s="4">
@@ -852,554 +809,253 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diseño y maquetación</t>
+          <t xml:space="preserve">Maquetación</t>
         </is>
       </c>
       <c r="B4" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programación</t>
+          <t xml:space="preserve">Game design</t>
         </is>
       </c>
       <c r="B5" s="4">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pruebas de juego</t>
+          <t xml:space="preserve">Programación</t>
         </is>
       </c>
       <c r="B6" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complejidad</t>
+          <t xml:space="preserve">Concepto</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multiplica las horas</t>
+          <t xml:space="preserve">Unidad</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horas</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baja · sencillo</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Media · medio</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta · complejo</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Muy alta</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qué incluye</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">sencilla</t>
-        </is>
-      </c>
-      <c r="B9" s="5">
-        <v>0.6</v>
+          <t xml:space="preserve">Prop</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prop</t>
+        </is>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Una pieza de arte. Baja: icono, viñeta, recoloreado. Media: objeto, nota, etiqueta. Alta: marco, dispositivo, personaje. Muy alta: ilustración o cuadro.</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">media</t>
-        </is>
-      </c>
-      <c r="B10" s="5">
-        <v>1</v>
+          <t xml:space="preserve">Maquetación</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juego</t>
+        </is>
+      </c>
+      <c r="C10" s="5">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montar las páginas del juego con sus piezas, textos y huecos, y comprobar que todo cabe.</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">compleja</t>
-        </is>
-      </c>
-      <c r="B11" s="5">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="12"/>
+          <t xml:space="preserve">Game design de un puzzle</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">puzzle</t>
+        </is>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="F11" s="5">
+        <v>7</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idear el puzzle: mecánica, pistas, solución y cómo encaja en la historia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Game design: testing</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prueba</t>
+        </is>
+      </c>
+      <c r="C12" s="5">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jugar el escape impreso de principio a fin y ajustar lo que falle.</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Concepto</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidad</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Horas (media)</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Qué incluye</t>
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programación de un puzzle</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">puzzle</t>
+        </is>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5">
+        <v>3</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montarlo en el creador: mecánica, campos del formulario y solución. Sencillo: del catálogo; complejo: mecánica nueva.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Icono</t>
+          <t xml:space="preserve">Programación: ajustes</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">pieza</t>
+          <t xml:space="preserve">ajuste</t>
         </is>
       </c>
       <c r="C14" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Icono de app, símbolo o viñeta: una forma sencilla, en los colores del juego.</t>
+        <v>1</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cambios pequeños: un campo, un tema de color, un texto calculado…</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objeto o asset pequeño</t>
+          <t xml:space="preserve">Otro trabajo</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">pieza</t>
+          <t xml:space="preserve">hora</t>
         </is>
       </c>
       <c r="C15" s="5">
-        <v>3</v>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lupa, regalo, sello, llave…: boceto, color y sombras.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Papel, nota o etiqueta</t>
-        </is>
-      </c>
-      <c r="B16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pieza</t>
-        </is>
-      </c>
-      <c r="C16" s="5">
-        <v>2</v>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nota kraft, papel rasgado, etiqueta con clip: textura y pliegues.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marco o ficha con hueco de foto</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pieza</t>
-        </is>
-      </c>
-      <c r="C17" s="5">
-        <v>3</v>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Polaroid, ficha de sospechoso: con la zona útil marcada para la foto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dispositivo con pantalla</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pieza</t>
-        </is>
-      </c>
-      <c r="C18" s="5">
-        <v>7</v>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Móvil, tableta, monitor: carcasa, pantalla y elementos de interfaz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Personaje</t>
-        </is>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pieza</t>
-        </is>
-      </c>
-      <c r="C19" s="5">
-        <v>8</v>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Retrato o figura de cuerpo entero, con expresión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ilustración o cuadro</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pieza</t>
-        </is>
-      </c>
-      <c r="C20" s="5">
-        <v>16</v>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Escena con personajes y fondo (como el cuadro de los perros jugando a las cartas).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fondo de página completa</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pieza</t>
-        </is>
-      </c>
-      <c r="C21" s="5">
-        <v>6</v>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fondo o composición que ocupa la página.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Variación de una pieza existente</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pieza</t>
-        </is>
-      </c>
-      <c r="C22" s="5">
-        <v>1</v>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cambiar un detalle, la forma o el tamaño de una pieza de la biblioteca.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Revisión de pieza recoloreada</t>
-        </is>
-      </c>
-      <c r="B23" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pieza</t>
-        </is>
-      </c>
-      <c r="C23" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cambio de tema: el creador recolorea solo; la ilustradora revisa cada pieza y retoca lo que no quede bien.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Página nueva</t>
-        </is>
-      </c>
-      <c r="B24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">página</t>
-        </is>
-      </c>
-      <c r="C24" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Maquetada con piezas de la biblioteca, con sus textos y huecos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ajuste de una página existente</t>
-        </is>
-      </c>
-      <c r="B25" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">página</t>
-        </is>
-      </c>
-      <c r="C25" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mover, cambiar o quitar elementos; revisar que todo cabe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Textos de una página (ES/EN)</t>
-        </is>
-      </c>
-      <c r="B26" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">página</t>
-        </is>
-      </c>
-      <c r="C26" s="5">
-        <v>1</v>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Redacción y traducción, y comprobar que caben en sus huecos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pregunta del formulario</t>
-        </is>
-      </c>
-      <c r="B27" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pregunta</t>
-        </is>
-      </c>
-      <c r="C27" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pregunta nueva con su tope, ayuda y ejemplos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cambio de tema de color</t>
-        </is>
-      </c>
-      <c r="B28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juego</t>
-        </is>
-      </c>
-      <c r="C28" s="5">
-        <v>3</v>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elegir la paleta, aplicarla en el creador y ajustar contrastes y legibilidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Puzzle del catálogo</t>
-        </is>
-      </c>
-      <c r="B29" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">puzzle</t>
-        </is>
-      </c>
-      <c r="C29" s="5">
-        <v>1</v>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La mecánica ya existe: configurarla, conectarla al formulario y comprobar la solución.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Puzzle de contenido</t>
-        </is>
-      </c>
-      <c r="B30" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">puzzle</t>
-        </is>
-      </c>
-      <c r="C30" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sin mecánica: textos, arte y solución montados en el creador.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mecánica nueva sencilla</t>
-        </is>
-      </c>
-      <c r="B31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mecánica</t>
-        </is>
-      </c>
-      <c r="C31" s="5">
-        <v>6</v>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Una regla nueva del motor: iniciales, prefijos, casillas marcadas…</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mecánica nueva compleja</t>
-        </is>
-      </c>
-      <c r="B32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mecánica</t>
-        </is>
-      </c>
-      <c r="C32" s="5">
-        <v>16</v>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiras recortables, cifrados, cuadrículas: con su validación y pruebas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Campo calculado</t>
-        </is>
-      </c>
-      <c r="B33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">campo</t>
-        </is>
-      </c>
-      <c r="C33" s="5">
-        <v>2</v>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Un dato que sale de otros (una suma, una palabra cifrada…).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prueba de un puzzle</t>
-        </is>
-      </c>
-      <c r="B34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">puzzle</t>
-        </is>
-      </c>
-      <c r="C34" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Imprimirlo y resolverlo en papel, con notas de lo que falla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prueba completa del juego</t>
-        </is>
-      </c>
-      <c r="B35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juego</t>
-        </is>
-      </c>
-      <c r="C35" s="5">
-        <v>3</v>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Una partida de principio a fin con el juego impreso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Otro trabajo</t>
-        </is>
-      </c>
-      <c r="B36" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hora</t>
-        </is>
-      </c>
-      <c r="C36" s="5">
-        <v>1</v>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Cualquier otra tarea, por horas.</t>
         </is>
